--- a/Prices.xlsx
+++ b/Prices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/285742b78a69f0d9/20. Personal/SerenaWellness/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE760C0-7312-4E2C-A4D5-630EB5A9ACC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{5EE760C0-7312-4E2C-A4D5-630EB5A9ACC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F49F7E7A-8673-4E05-ABEB-88CF17FA81D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E90C3D68-B754-4B65-814B-6F475C9455AE}"/>
   </bookViews>
@@ -146,9 +146,6 @@
     </r>
   </si>
   <si>
-    <t>€ 60</t>
-  </si>
-  <si>
     <t>Lezione di Yoga (3-10 persone)</t>
   </si>
   <si>
@@ -284,10 +281,13 @@
     <t>Lezione di Pilates (+11 persone)</t>
   </si>
   <si>
-    <t>€ 90</t>
-  </si>
-  <si>
     <t>€ 50</t>
+  </si>
+  <si>
+    <t>€ 80</t>
+  </si>
+  <si>
+    <t>€ 120</t>
   </si>
 </sst>
 </file>
@@ -700,7 +700,7 @@
         <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -742,7 +742,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -756,7 +756,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -770,7 +770,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -798,7 +798,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -812,7 +812,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -826,7 +826,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -840,7 +840,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -854,7 +854,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -868,7 +868,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -882,7 +882,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -896,7 +896,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -904,13 +904,13 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -918,71 +918,71 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
       <c r="C18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1018,7 +1018,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -1033,7 +1033,7 @@
         <v>5</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1049,7 +1049,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1065,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1081,7 +1081,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1113,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1143,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1157,7 +1157,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1171,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1185,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1199,7 +1199,7 @@
         <v>28</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1221,13 +1221,13 @@
         <v>23</v>
       </c>
       <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1235,18 +1235,18 @@
         <v>23</v>
       </c>
       <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
@@ -1255,12 +1255,12 @@
         <v>28</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
@@ -1274,30 +1274,30 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
